--- a/BASE DE KPI CCOT.xlsx
+++ b/BASE DE KPI CCOT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://claromovilco-my.sharepoint.com/personal/38101279_claro_com_co/Documents/KPI_WEB/dashboard_kpi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300B9941-CD30-4FD0-A9B7-CAB5BFA365A0}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5853C7F7-2C34-4364-AD4A-DCA159A3623E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BE94DC4F-BEA5-40A0-AFC4-A749FDC05493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE94DC4F-BEA5-40A0-AFC4-A749FDC05493}"/>
   </bookViews>
   <sheets>
     <sheet name="LOLY" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
   <si>
     <t>USUARIO</t>
   </si>
@@ -179,15 +179,9 @@
     <t>R1</t>
   </si>
   <si>
-    <t>REALIZADO enero 2026</t>
-  </si>
-  <si>
     <t>CUMPLIMIENTO ENERO 2026</t>
   </si>
   <si>
-    <t>REALIZADO enero 2027</t>
-  </si>
-  <si>
     <t>CUMPLIMIENTO MARZO 2026</t>
   </si>
   <si>
@@ -206,7 +200,7 @@
     <t>CUMPLIMIENTO ABRIL 2026</t>
   </si>
   <si>
-    <t>CUMPLIMIENTO MAYO 2026</t>
+    <t>REALIZADO ENERO 2026</t>
   </si>
 </sst>
 </file>
@@ -719,9 +713,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -759,7 +753,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -865,7 +859,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1007,7 +1001,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1015,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C26F226A-4210-49D6-9450-2660EE9C0429}">
-  <dimension ref="B1:AK19"/>
+  <dimension ref="B1:AG19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -1033,7 +1027,7 @@
     <col min="21" max="21" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -1042,7 +1036,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="2:37" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:33" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1105,52 +1099,40 @@
         <v>5</v>
       </c>
       <c r="W2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="Y2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AB2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AD2" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AE2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AG2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ2" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="3" spans="2:37" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:33" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>15</v>
       </c>
@@ -1229,8 +1211,17 @@
         <f>W3/$K3</f>
         <v>0.75875555555555563</v>
       </c>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="19"/>
     </row>
-    <row r="4" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>19</v>
       </c>
@@ -1302,15 +1293,22 @@
         <f>W4/$V4</f>
         <v>0.97666666666666668</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="4">
         <v>0.3</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="4">
         <f>X4*Y4</f>
         <v>0.29299999999999998</v>
       </c>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="24"/>
     </row>
-    <row r="5" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
@@ -1382,15 +1380,22 @@
         <f>W5/$V5</f>
         <v>0.45888888888888885</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="4">
         <v>0.3</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="4">
         <f>X5*Y5</f>
         <v>0.13766666666666666</v>
       </c>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="25"/>
     </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>25</v>
       </c>
@@ -1462,11 +1467,19 @@
         <f>W6/$V6</f>
         <v>0.91555555555555546</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="4">
         <v>0.2</v>
       </c>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="24"/>
     </row>
-    <row r="7" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
         <v>28</v>
       </c>
@@ -1538,15 +1551,22 @@
         <f>W7/$V7</f>
         <v>0.9297777777777777</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="4">
         <v>0.2</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="4">
         <f>X7*Y7</f>
         <v>0.18595555555555554</v>
       </c>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="24"/>
     </row>
-    <row r="8" spans="2:37" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:33" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
         <v>15</v>
       </c>
@@ -1625,8 +1645,17 @@
         <f>W8/$K8</f>
         <v>0.95901515151515149</v>
       </c>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="11"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="11"/>
     </row>
-    <row r="9" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
         <v>25</v>
       </c>
@@ -1698,8 +1727,17 @@
         <f>$T$9/V9</f>
         <v>1.0416666666666667</v>
       </c>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="28"/>
     </row>
-    <row r="10" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>28</v>
       </c>
@@ -1772,8 +1810,17 @@
         <f>$T$10/V10</f>
         <v>0.87636363636363623</v>
       </c>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="32"/>
+      <c r="AG10" s="28"/>
     </row>
-    <row r="11" spans="2:37" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:33" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="33" t="s">
         <v>15</v>
       </c>
@@ -1853,8 +1900,17 @@
         <f>W11/$K11</f>
         <v>0.96722222222222221</v>
       </c>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="11"/>
     </row>
-    <row r="12" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>36</v>
       </c>
@@ -1926,8 +1982,17 @@
         <f>$T12/V12</f>
         <v>0.97333333333333327</v>
       </c>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="28"/>
     </row>
-    <row r="13" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="21" t="s">
         <v>22</v>
       </c>
@@ -1999,8 +2064,17 @@
         <f>$T13/V13</f>
         <v>0.96111111111111103</v>
       </c>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="28"/>
     </row>
-    <row r="14" spans="2:37" s="20" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:33" s="20" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
         <v>15</v>
       </c>
@@ -2079,8 +2153,17 @@
         <f>W14/$K14</f>
         <v>0.9539331332855856</v>
       </c>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="11"/>
+      <c r="AB14" s="16"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="11"/>
     </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="21" t="s">
         <v>36</v>
       </c>
@@ -2152,8 +2235,17 @@
         <f>$T15/V15</f>
         <v>0.9076249999999999</v>
       </c>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="23"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="28"/>
     </row>
-    <row r="16" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="21" t="s">
         <v>22</v>
       </c>
@@ -2225,8 +2317,17 @@
         <f>W16/V16</f>
         <v>0.97912499999999991</v>
       </c>
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="39"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="38"/>
+      <c r="AF16" s="39"/>
+      <c r="AG16" s="28"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
         <v>33</v>
       </c>
@@ -2298,8 +2399,17 @@
         <f>$T17/V17</f>
         <v>0.98966436985996875</v>
       </c>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="23"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="23"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="28"/>
     </row>
-    <row r="18" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
         <v>33</v>
       </c>
@@ -2372,8 +2482,17 @@
         <f>$T18/V18</f>
         <v>1.0026669629958884</v>
       </c>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="40"/>
     </row>
-    <row r="19" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>15</v>
       </c>

--- a/BASE DE KPI CCOT.xlsx
+++ b/BASE DE KPI CCOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://claromovilco-my.sharepoint.com/personal/38101279_claro_com_co/Documents/KPI_WEB/dashboard_kpi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5853C7F7-2C34-4364-AD4A-DCA159A3623E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D284EC-818B-4B26-A6A3-FCAF4BD60385}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE94DC4F-BEA5-40A0-AFC4-A749FDC05493}"/>
   </bookViews>
@@ -710,6 +710,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1211,12 +1215,26 @@
         <f>W3/$K3</f>
         <v>0.75875555555555563</v>
       </c>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="17"/>
-      <c r="AD3" s="19"/>
+      <c r="Y3" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="19">
+        <f>Z3/$K3</f>
+        <v>1</v>
+      </c>
+      <c r="AB3" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="17">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="19">
+        <f>AC3/$K3</f>
+        <v>1</v>
+      </c>
       <c r="AE3" s="17"/>
       <c r="AF3" s="17"/>
       <c r="AG3" s="19"/>
@@ -1294,15 +1312,23 @@
         <v>0.97666666666666668</v>
       </c>
       <c r="Y4" s="4">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Z4" s="4">
         <f>X4*Y4</f>
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
+        <v>0.879</v>
+      </c>
+      <c r="AA4" s="24">
+        <f>Z4/$V4</f>
+        <v>0.97666666666666668</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC4" s="4">
+        <f>AA4*AB4</f>
+        <v>0.879</v>
+      </c>
       <c r="AD4" s="24"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
@@ -1381,15 +1407,23 @@
         <v>0.45888888888888885</v>
       </c>
       <c r="Y5" s="4">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Z5" s="4">
         <f>X5*Y5</f>
-        <v>0.13766666666666666</v>
-      </c>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="AA5" s="25">
+        <f>Z5/$V5</f>
+        <v>0.45888888888888885</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC5" s="4">
+        <f>AA5*AB5</f>
+        <v>0.41299999999999998</v>
+      </c>
       <c r="AD5" s="25"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
@@ -1468,12 +1502,23 @@
         <v>0.91555555555555546</v>
       </c>
       <c r="Y6" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
+        <v>0.9</v>
+      </c>
+      <c r="Z6" s="4">
+        <f>X6*Y6</f>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="AA6" s="24">
+        <f>Z6/$V6</f>
+        <v>0.91555555555555546</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC6" s="4">
+        <f>AA6*AB6</f>
+        <v>0.82399999999999995</v>
+      </c>
       <c r="AD6" s="24"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
@@ -1552,15 +1597,23 @@
         <v>0.9297777777777777</v>
       </c>
       <c r="Y7" s="4">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Z7" s="4">
         <f>X7*Y7</f>
-        <v>0.18595555555555554</v>
-      </c>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
+        <v>0.83679999999999999</v>
+      </c>
+      <c r="AA7" s="24">
+        <f>Z7/$V7</f>
+        <v>0.9297777777777777</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC7" s="4">
+        <f>AA7*AB7</f>
+        <v>0.83679999999999999</v>
+      </c>
       <c r="AD7" s="24"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
@@ -1645,9 +1698,16 @@
         <f>W8/$K8</f>
         <v>0.95901515151515149</v>
       </c>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="11"/>
+      <c r="Y8" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="11">
+        <f>Z8/$K8</f>
+        <v>1</v>
+      </c>
       <c r="AB8" s="17"/>
       <c r="AC8" s="17"/>
       <c r="AD8" s="11"/>
@@ -1727,9 +1787,17 @@
         <f>$T$9/V9</f>
         <v>1.0416666666666667</v>
       </c>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="28"/>
+      <c r="Y9" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" ref="Z9:Z10" si="0">X9*Y9</f>
+        <v>0.93750000000000011</v>
+      </c>
+      <c r="AA9" s="28">
+        <f>$T$9/Y9</f>
+        <v>0.69444444444444442</v>
+      </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="28"/>
@@ -1810,9 +1878,17 @@
         <f>$T$10/V10</f>
         <v>0.87636363636363623</v>
       </c>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="28"/>
+      <c r="Y10" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.78872727272727261</v>
+      </c>
+      <c r="AA10" s="28">
+        <f>$T$10/Y10</f>
+        <v>0.53555555555555556</v>
+      </c>
       <c r="AB10" s="32"/>
       <c r="AC10" s="32"/>
       <c r="AD10" s="28"/>
@@ -1900,9 +1976,16 @@
         <f>W11/$K11</f>
         <v>0.96722222222222221</v>
       </c>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="11"/>
+      <c r="Y11" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="11">
+        <f>Z11/$K11</f>
+        <v>1</v>
+      </c>
       <c r="AB11" s="16"/>
       <c r="AC11" s="16"/>
       <c r="AD11" s="11"/>
@@ -1982,9 +2065,17 @@
         <f>$T12/V12</f>
         <v>0.97333333333333327</v>
       </c>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="28"/>
+      <c r="Y12" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" ref="Z12:Z13" si="1">X12*Y12</f>
+        <v>0.876</v>
+      </c>
+      <c r="AA12" s="28">
+        <f>$T12/Y12</f>
+        <v>0.97333333333333327</v>
+      </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="28"/>
@@ -2064,9 +2155,17 @@
         <f>$T13/V13</f>
         <v>0.96111111111111103</v>
       </c>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="28"/>
+      <c r="Y13" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="AA13" s="28">
+        <f>$T13/Y13</f>
+        <v>0.96111111111111103</v>
+      </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="28"/>
@@ -2153,9 +2252,16 @@
         <f>W14/$K14</f>
         <v>0.9539331332855856</v>
       </c>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="11"/>
+      <c r="Y14" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="11">
+        <f>Z14/$K14</f>
+        <v>1</v>
+      </c>
       <c r="AB14" s="16"/>
       <c r="AC14" s="16"/>
       <c r="AD14" s="11"/>
@@ -2235,9 +2341,17 @@
         <f>$T15/V15</f>
         <v>0.9076249999999999</v>
       </c>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="28"/>
+      <c r="Y15" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z15" s="4">
+        <f t="shared" ref="Z15:Z18" si="2">X15*Y15</f>
+        <v>0.81686249999999994</v>
+      </c>
+      <c r="AA15" s="28">
+        <f>$T15/Y15</f>
+        <v>0.8067777777777777</v>
+      </c>
       <c r="AB15" s="23"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="28"/>
@@ -2317,9 +2431,17 @@
         <f>W16/V16</f>
         <v>0.97912499999999991</v>
       </c>
-      <c r="Y16" s="38"/>
-      <c r="Z16" s="39"/>
-      <c r="AA16" s="28"/>
+      <c r="Y16" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z16" s="4">
+        <f t="shared" si="2"/>
+        <v>0.88121249999999995</v>
+      </c>
+      <c r="AA16" s="28">
+        <f>Z16/Y16</f>
+        <v>0.97912499999999991</v>
+      </c>
       <c r="AB16" s="38"/>
       <c r="AC16" s="39"/>
       <c r="AD16" s="28"/>
@@ -2399,9 +2521,17 @@
         <f>$T17/V17</f>
         <v>0.98966436985996875</v>
       </c>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="28"/>
+      <c r="Y17" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z17" s="4">
+        <f t="shared" si="2"/>
+        <v>0.89069793287397192</v>
+      </c>
+      <c r="AA17" s="28">
+        <f>$T17/Y17</f>
+        <v>0.98944444444444435</v>
+      </c>
       <c r="AB17" s="23"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="28"/>
@@ -2482,9 +2612,17 @@
         <f>$T18/V18</f>
         <v>1.0026669629958884</v>
       </c>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="31"/>
-      <c r="AA18" s="40"/>
+      <c r="Y18" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="Z18" s="4">
+        <f t="shared" si="2"/>
+        <v>0.90240026669629958</v>
+      </c>
+      <c r="AA18" s="40">
+        <f>$T18/Y18</f>
+        <v>1.0025555555555554</v>
+      </c>
       <c r="AB18" s="31"/>
       <c r="AC18" s="31"/>
       <c r="AD18" s="40"/>

--- a/BASE DE KPI CCOT.xlsx
+++ b/BASE DE KPI CCOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://claromovilco-my.sharepoint.com/personal/38101279_claro_com_co/Documents/KPI_WEB/dashboard_kpi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D284EC-818B-4B26-A6A3-FCAF4BD60385}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83724031-EB55-40BC-8189-601CF4FED7DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE94DC4F-BEA5-40A0-AFC4-A749FDC05493}"/>
   </bookViews>
@@ -1329,7 +1329,10 @@
         <f>AA4*AB4</f>
         <v>0.879</v>
       </c>
-      <c r="AD4" s="24"/>
+      <c r="AD4" s="24">
+        <f>AC4/$V4</f>
+        <v>0.97666666666666668</v>
+      </c>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="24"/>
@@ -1424,7 +1427,10 @@
         <f>AA5*AB5</f>
         <v>0.41299999999999998</v>
       </c>
-      <c r="AD5" s="25"/>
+      <c r="AD5" s="25">
+        <f>AC5/$V5</f>
+        <v>0.45888888888888885</v>
+      </c>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="25"/>
@@ -1519,7 +1525,10 @@
         <f>AA6*AB6</f>
         <v>0.82399999999999995</v>
       </c>
-      <c r="AD6" s="24"/>
+      <c r="AD6" s="24">
+        <f>AC6/$V6</f>
+        <v>0.91555555555555546</v>
+      </c>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="24"/>
@@ -1614,7 +1623,10 @@
         <f>AA7*AB7</f>
         <v>0.83679999999999999</v>
       </c>
-      <c r="AD7" s="24"/>
+      <c r="AD7" s="24">
+        <f>AC7/$V7</f>
+        <v>0.9297777777777777</v>
+      </c>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="24"/>
@@ -1708,9 +1720,16 @@
         <f>Z8/$K8</f>
         <v>1</v>
       </c>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="11"/>
+      <c r="AB8" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="17">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="11">
+        <f>AC8/$K8</f>
+        <v>1</v>
+      </c>
       <c r="AE8" s="17"/>
       <c r="AF8" s="17"/>
       <c r="AG8" s="11"/>
@@ -1798,9 +1817,17 @@
         <f>$T$9/Y9</f>
         <v>0.69444444444444442</v>
       </c>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="28"/>
+      <c r="AB9" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC9" s="4">
+        <f t="shared" ref="AC9:AC10" si="1">AA9*AB9</f>
+        <v>0.625</v>
+      </c>
+      <c r="AD9" s="28">
+        <f>$T$9/AB9</f>
+        <v>0.69444444444444442</v>
+      </c>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="28"/>
@@ -1889,9 +1916,17 @@
         <f>$T$10/Y10</f>
         <v>0.53555555555555556</v>
       </c>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="28"/>
+      <c r="AB10" s="32">
+        <v>0.9</v>
+      </c>
+      <c r="AC10" s="32">
+        <f t="shared" si="1"/>
+        <v>0.48200000000000004</v>
+      </c>
+      <c r="AD10" s="28">
+        <f>$T$10/AB10</f>
+        <v>0.53555555555555556</v>
+      </c>
       <c r="AE10" s="32"/>
       <c r="AF10" s="32"/>
       <c r="AG10" s="28"/>
@@ -1986,9 +2021,16 @@
         <f>Z11/$K11</f>
         <v>1</v>
       </c>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="11"/>
+      <c r="AB11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="11">
+        <f>AC11/$K11</f>
+        <v>1</v>
+      </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16"/>
       <c r="AG11" s="11"/>
@@ -2069,16 +2111,24 @@
         <v>0.9</v>
       </c>
       <c r="Z12" s="4">
-        <f t="shared" ref="Z12:Z13" si="1">X12*Y12</f>
+        <f t="shared" ref="Z12:Z13" si="2">X12*Y12</f>
         <v>0.876</v>
       </c>
       <c r="AA12" s="28">
         <f>$T12/Y12</f>
         <v>0.97333333333333327</v>
       </c>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="28"/>
+      <c r="AB12" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC12" s="4">
+        <f t="shared" ref="AC12:AC13" si="3">AA12*AB12</f>
+        <v>0.876</v>
+      </c>
+      <c r="AD12" s="28">
+        <f>$T12/AB12</f>
+        <v>0.97333333333333327</v>
+      </c>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="28"/>
@@ -2159,16 +2209,24 @@
         <v>0.9</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.86499999999999999</v>
       </c>
       <c r="AA13" s="28">
         <f>$T13/Y13</f>
         <v>0.96111111111111103</v>
       </c>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="28"/>
+      <c r="AB13" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AC13" s="4">
+        <f t="shared" si="3"/>
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="AD13" s="28">
+        <f>$T13/AB13</f>
+        <v>0.96111111111111103</v>
+      </c>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="28"/>
@@ -2262,9 +2320,16 @@
         <f>Z14/$K14</f>
         <v>1</v>
       </c>
-      <c r="AB14" s="16"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="11"/>
+      <c r="AB14" s="16">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="16">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="11">
+        <f>AC14/$K14</f>
+        <v>1</v>
+      </c>
       <c r="AE14" s="16"/>
       <c r="AF14" s="16"/>
       <c r="AG14" s="11"/>
@@ -2345,16 +2410,24 @@
         <v>0.9</v>
       </c>
       <c r="Z15" s="4">
-        <f t="shared" ref="Z15:Z18" si="2">X15*Y15</f>
+        <f t="shared" ref="Z15:Z18" si="4">X15*Y15</f>
         <v>0.81686249999999994</v>
       </c>
       <c r="AA15" s="28">
         <f>$T15/Y15</f>
         <v>0.8067777777777777</v>
       </c>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="28"/>
+      <c r="AB15" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="AC15" s="4">
+        <f t="shared" ref="AC15:AC18" si="5">AA15*AB15</f>
+        <v>0.72609999999999997</v>
+      </c>
+      <c r="AD15" s="28">
+        <f>$T15/AB15</f>
+        <v>0.8067777777777777</v>
+      </c>
       <c r="AE15" s="23"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="28"/>
@@ -2435,16 +2508,24 @@
         <v>0.9</v>
       </c>
       <c r="Z16" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.88121249999999995</v>
       </c>
       <c r="AA16" s="28">
         <f>Z16/Y16</f>
         <v>0.97912499999999991</v>
       </c>
-      <c r="AB16" s="38"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="28"/>
+      <c r="AB16" s="38">
+        <v>0.9</v>
+      </c>
+      <c r="AC16" s="39">
+        <f t="shared" si="5"/>
+        <v>0.88121249999999995</v>
+      </c>
+      <c r="AD16" s="28">
+        <f>AC16/AB16</f>
+        <v>0.97912499999999991</v>
+      </c>
       <c r="AE16" s="38"/>
       <c r="AF16" s="39"/>
       <c r="AG16" s="28"/>
@@ -2525,16 +2606,24 @@
         <v>0.9</v>
       </c>
       <c r="Z17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.89069793287397192</v>
       </c>
       <c r="AA17" s="28">
         <f>$T17/Y17</f>
         <v>0.98944444444444435</v>
       </c>
-      <c r="AB17" s="23"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="28"/>
+      <c r="AB17" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="AC17" s="4">
+        <f t="shared" si="5"/>
+        <v>0.89049999999999996</v>
+      </c>
+      <c r="AD17" s="28">
+        <f>$T17/AB17</f>
+        <v>0.98944444444444435</v>
+      </c>
       <c r="AE17" s="23"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="28"/>
@@ -2616,16 +2705,24 @@
         <v>0.9</v>
       </c>
       <c r="Z18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.90240026669629958</v>
       </c>
       <c r="AA18" s="40">
         <f>$T18/Y18</f>
         <v>1.0025555555555554</v>
       </c>
-      <c r="AB18" s="31"/>
-      <c r="AC18" s="31"/>
-      <c r="AD18" s="40"/>
+      <c r="AB18" s="31">
+        <v>0.9</v>
+      </c>
+      <c r="AC18" s="31">
+        <f t="shared" si="5"/>
+        <v>0.90229999999999988</v>
+      </c>
+      <c r="AD18" s="40">
+        <f>$T18/AB18</f>
+        <v>1.0025555555555554</v>
+      </c>
       <c r="AE18" s="31"/>
       <c r="AF18" s="31"/>
       <c r="AG18" s="40"/>

--- a/BASE DE KPI CCOT.xlsx
+++ b/BASE DE KPI CCOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://claromovilco-my.sharepoint.com/personal/38101279_claro_com_co/Documents/KPI_WEB/dashboard_kpi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83724031-EB55-40BC-8189-601CF4FED7DF}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A181438D-E28A-4CF7-8823-3D0B0EC32396}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE94DC4F-BEA5-40A0-AFC4-A749FDC05493}"/>
   </bookViews>
@@ -710,10 +710,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1235,9 +1231,16 @@
         <f>AC3/$K3</f>
         <v>1</v>
       </c>
-      <c r="AE3" s="17"/>
-      <c r="AF3" s="17"/>
-      <c r="AG3" s="19"/>
+      <c r="AE3" s="17">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="17">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="19">
+        <f>AF3/$K3</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
@@ -1333,9 +1336,17 @@
         <f>AC4/$V4</f>
         <v>0.97666666666666668</v>
       </c>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="24"/>
+      <c r="AE4" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF4" s="4">
+        <f>AD4*AE4</f>
+        <v>0.879</v>
+      </c>
+      <c r="AG4" s="24">
+        <f>AF4/$V4</f>
+        <v>0.97666666666666668</v>
+      </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
@@ -1431,9 +1442,17 @@
         <f>AC5/$V5</f>
         <v>0.45888888888888885</v>
       </c>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
-      <c r="AG5" s="25"/>
+      <c r="AE5" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF5" s="4">
+        <f>AD5*AE5</f>
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="AG5" s="25">
+        <f>AF5/$V5</f>
+        <v>0.45888888888888885</v>
+      </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
@@ -1529,9 +1548,17 @@
         <f>AC6/$V6</f>
         <v>0.91555555555555546</v>
       </c>
-      <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
-      <c r="AG6" s="24"/>
+      <c r="AE6" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF6" s="4">
+        <f>AD6*AE6</f>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="AG6" s="24">
+        <f>AF6/$V6</f>
+        <v>0.91555555555555546</v>
+      </c>
     </row>
     <row r="7" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
@@ -1627,9 +1654,17 @@
         <f>AC7/$V7</f>
         <v>0.9297777777777777</v>
       </c>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
-      <c r="AG7" s="24"/>
+      <c r="AE7" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF7" s="4">
+        <f>AD7*AE7</f>
+        <v>0.83679999999999999</v>
+      </c>
+      <c r="AG7" s="24">
+        <f>AF7/$V7</f>
+        <v>0.9297777777777777</v>
+      </c>
     </row>
     <row r="8" spans="2:33" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
@@ -1730,9 +1765,16 @@
         <f>AC8/$K8</f>
         <v>1</v>
       </c>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="11"/>
+      <c r="AE8" s="17">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="17">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="11">
+        <f>AF8/$K8</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
@@ -1828,9 +1870,17 @@
         <f>$T$9/AB9</f>
         <v>0.69444444444444442</v>
       </c>
-      <c r="AE9" s="4"/>
-      <c r="AF9" s="4"/>
-      <c r="AG9" s="28"/>
+      <c r="AE9" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF9" s="4">
+        <f t="shared" ref="AF9:AF10" si="2">AD9*AE9</f>
+        <v>0.625</v>
+      </c>
+      <c r="AG9" s="28">
+        <f>$T$9/AE9</f>
+        <v>0.69444444444444442</v>
+      </c>
     </row>
     <row r="10" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
@@ -1927,9 +1977,17 @@
         <f>$T$10/AB10</f>
         <v>0.53555555555555556</v>
       </c>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="32"/>
-      <c r="AG10" s="28"/>
+      <c r="AE10" s="32">
+        <v>0.9</v>
+      </c>
+      <c r="AF10" s="32">
+        <f t="shared" si="2"/>
+        <v>0.48200000000000004</v>
+      </c>
+      <c r="AG10" s="28">
+        <f>$T$10/AE10</f>
+        <v>0.53555555555555556</v>
+      </c>
     </row>
     <row r="11" spans="2:33" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="33" t="s">
@@ -2031,9 +2089,16 @@
         <f>AC11/$K11</f>
         <v>1</v>
       </c>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="11"/>
+      <c r="AE11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="11">
+        <f>AF11/$K11</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
@@ -2111,7 +2176,7 @@
         <v>0.9</v>
       </c>
       <c r="Z12" s="4">
-        <f t="shared" ref="Z12:Z13" si="2">X12*Y12</f>
+        <f t="shared" ref="Z12:Z13" si="3">X12*Y12</f>
         <v>0.876</v>
       </c>
       <c r="AA12" s="28">
@@ -2122,16 +2187,24 @@
         <v>0.9</v>
       </c>
       <c r="AC12" s="4">
-        <f t="shared" ref="AC12:AC13" si="3">AA12*AB12</f>
+        <f t="shared" ref="AC12:AC13" si="4">AA12*AB12</f>
         <v>0.876</v>
       </c>
       <c r="AD12" s="28">
         <f>$T12/AB12</f>
         <v>0.97333333333333327</v>
       </c>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
-      <c r="AG12" s="28"/>
+      <c r="AE12" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF12" s="4">
+        <f t="shared" ref="AF12:AF13" si="5">AD12*AE12</f>
+        <v>0.876</v>
+      </c>
+      <c r="AG12" s="28">
+        <f>$T12/AE12</f>
+        <v>0.97333333333333327</v>
+      </c>
     </row>
     <row r="13" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="21" t="s">
@@ -2209,7 +2282,7 @@
         <v>0.9</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.86499999999999999</v>
       </c>
       <c r="AA13" s="28">
@@ -2220,16 +2293,24 @@
         <v>0.9</v>
       </c>
       <c r="AC13" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.86499999999999999</v>
       </c>
       <c r="AD13" s="28">
         <f>$T13/AB13</f>
         <v>0.96111111111111103</v>
       </c>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="4"/>
-      <c r="AG13" s="28"/>
+      <c r="AE13" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="AF13" s="4">
+        <f t="shared" si="5"/>
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="AG13" s="28">
+        <f>$T13/AE13</f>
+        <v>0.96111111111111103</v>
+      </c>
     </row>
     <row r="14" spans="2:33" s="20" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
@@ -2330,9 +2411,16 @@
         <f>AC14/$K14</f>
         <v>1</v>
       </c>
-      <c r="AE14" s="16"/>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="11"/>
+      <c r="AE14" s="16">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="16">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="11">
+        <f>AF14/$K14</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="21" t="s">
@@ -2410,7 +2498,7 @@
         <v>0.9</v>
       </c>
       <c r="Z15" s="4">
-        <f t="shared" ref="Z15:Z18" si="4">X15*Y15</f>
+        <f t="shared" ref="Z15:Z18" si="6">X15*Y15</f>
         <v>0.81686249999999994</v>
       </c>
       <c r="AA15" s="28">
@@ -2421,16 +2509,24 @@
         <v>0.9</v>
       </c>
       <c r="AC15" s="4">
-        <f t="shared" ref="AC15:AC18" si="5">AA15*AB15</f>
+        <f t="shared" ref="AC15:AC18" si="7">AA15*AB15</f>
         <v>0.72609999999999997</v>
       </c>
       <c r="AD15" s="28">
         <f>$T15/AB15</f>
         <v>0.8067777777777777</v>
       </c>
-      <c r="AE15" s="23"/>
-      <c r="AF15" s="4"/>
-      <c r="AG15" s="28"/>
+      <c r="AE15" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="AF15" s="4">
+        <f t="shared" ref="AF15:AF18" si="8">AD15*AE15</f>
+        <v>0.72609999999999997</v>
+      </c>
+      <c r="AG15" s="28">
+        <f>$T15/AE15</f>
+        <v>0.8067777777777777</v>
+      </c>
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="21" t="s">
@@ -2508,7 +2604,7 @@
         <v>0.9</v>
       </c>
       <c r="Z16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.88121249999999995</v>
       </c>
       <c r="AA16" s="28">
@@ -2519,16 +2615,24 @@
         <v>0.9</v>
       </c>
       <c r="AC16" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.88121249999999995</v>
       </c>
       <c r="AD16" s="28">
         <f>AC16/AB16</f>
         <v>0.97912499999999991</v>
       </c>
-      <c r="AE16" s="38"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="28"/>
+      <c r="AE16" s="38">
+        <v>0.9</v>
+      </c>
+      <c r="AF16" s="39">
+        <f t="shared" si="8"/>
+        <v>0.88121249999999995</v>
+      </c>
+      <c r="AG16" s="28">
+        <f>AF16/AE16</f>
+        <v>0.97912499999999991</v>
+      </c>
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
@@ -2606,7 +2710,7 @@
         <v>0.9</v>
       </c>
       <c r="Z17" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.89069793287397192</v>
       </c>
       <c r="AA17" s="28">
@@ -2617,16 +2721,24 @@
         <v>0.9</v>
       </c>
       <c r="AC17" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.89049999999999996</v>
       </c>
       <c r="AD17" s="28">
         <f>$T17/AB17</f>
         <v>0.98944444444444435</v>
       </c>
-      <c r="AE17" s="23"/>
-      <c r="AF17" s="4"/>
-      <c r="AG17" s="28"/>
+      <c r="AE17" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="AF17" s="4">
+        <f t="shared" si="8"/>
+        <v>0.89049999999999996</v>
+      </c>
+      <c r="AG17" s="28">
+        <f>$T17/AE17</f>
+        <v>0.98944444444444435</v>
+      </c>
     </row>
     <row r="18" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
@@ -2705,7 +2817,7 @@
         <v>0.9</v>
       </c>
       <c r="Z18" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.90240026669629958</v>
       </c>
       <c r="AA18" s="40">
@@ -2716,16 +2828,24 @@
         <v>0.9</v>
       </c>
       <c r="AC18" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.90229999999999988</v>
       </c>
       <c r="AD18" s="40">
         <f>$T18/AB18</f>
         <v>1.0025555555555554</v>
       </c>
-      <c r="AE18" s="31"/>
-      <c r="AF18" s="31"/>
-      <c r="AG18" s="40"/>
+      <c r="AE18" s="31">
+        <v>0.9</v>
+      </c>
+      <c r="AF18" s="31">
+        <f t="shared" si="8"/>
+        <v>0.90229999999999988</v>
+      </c>
+      <c r="AG18" s="40">
+        <f>$T18/AE18</f>
+        <v>1.0025555555555554</v>
+      </c>
     </row>
     <row r="19" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">

--- a/BASE DE KPI CCOT.xlsx
+++ b/BASE DE KPI CCOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://claromovilco-my.sharepoint.com/personal/38101279_claro_com_co/Documents/KPI_WEB/dashboard_kpi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A181438D-E28A-4CF7-8823-3D0B0EC32396}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{D9399BA0-F83E-4062-8B2F-6176C2BFD55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2869BC1-CD16-484E-B4F2-52FC47D93627}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE94DC4F-BEA5-40A0-AFC4-A749FDC05493}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>USUARIO</t>
   </si>
@@ -149,9 +149,6 @@
     <t>R1-% Primer Agenda Trabajos I&amp;M</t>
   </si>
   <si>
-    <t>Jaime.Moreno.T</t>
-  </si>
-  <si>
     <t xml:space="preserve">  R1-Primer Agenda Trabajos UMM</t>
   </si>
   <si>
@@ -171,12 +168,6 @@
   </si>
   <si>
     <t xml:space="preserve">  R1-Efectividad Trabajos Movil</t>
-  </si>
-  <si>
-    <t>R1-Mejora Tiempos Ejecución trabajos OTC</t>
-  </si>
-  <si>
-    <t>R1</t>
   </si>
   <si>
     <t>CUMPLIMIENTO ENERO 2026</t>
@@ -207,11 +198,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,19 +260,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,18 +319,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
-        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -493,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -607,19 +579,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1009,12 +968,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C26F226A-4210-49D6-9450-2660EE9C0429}">
-  <dimension ref="B1:AG19"/>
+  <dimension ref="B1:AG18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
     <col min="4" max="4" width="40.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
@@ -1099,37 +1058,37 @@
         <v>5</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Y2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AB2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AD2" s="12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AE2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AG2" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="2:33" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2102,13 +2061,13 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>1300281</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>17</v>
@@ -2214,7 +2173,7 @@
         <v>1333782</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>17</v>
@@ -2320,7 +2279,7 @@
         <v>1345901</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>17</v>
@@ -2424,13 +2383,13 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="21" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>1315424</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -2536,7 +2495,7 @@
         <v>1333776</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -2636,13 +2595,13 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -2742,13 +2701,13 @@
     </row>
     <row r="18" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" s="30" t="s">
         <v>17</v>
@@ -2847,39 +2806,8 @@
         <v>1.0025555555555554</v>
       </c>
     </row>
-    <row r="19" spans="2:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="27">
-        <v>1334754</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="43">
-        <v>99.142556068076985</v>
-      </c>
-      <c r="K19" s="43"/>
-      <c r="L19" s="44">
-        <v>94.225430000000003</v>
-      </c>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="45">
-        <v>95</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;6&amp;K000000 Clasificación: Uso Interno. Documento Claro Colombia</oddFooter>
